--- a/artfynd/A 47044-2025 artfynd.xlsx
+++ b/artfynd/A 47044-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131894964</v>
+        <v>131894860</v>
       </c>
       <c r="B2" t="n">
-        <v>57903</v>
+        <v>57825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,24 +709,19 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pajsoån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480450</v>
+        <v>480343</v>
       </c>
       <c r="R2" t="n">
-        <v>6674189</v>
+        <v>6674339</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,14 +755,14 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Dun nära funnen dödad tjädertupp</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131894860</v>
+        <v>131894964</v>
       </c>
       <c r="B3" t="n">
-        <v>57824</v>
+        <v>57904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -821,19 +816,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pajsoån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480343</v>
+        <v>480450</v>
       </c>
       <c r="R3" t="n">
-        <v>6674339</v>
+        <v>6674189</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,14 +867,14 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Dun nära funnen dödad tjädertupp</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>131894809</v>
       </c>
       <c r="B4" t="n">
-        <v>57082</v>
+        <v>57083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131894922</v>
       </c>
       <c r="B5" t="n">
-        <v>57091</v>
+        <v>57092</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47044-2025 artfynd.xlsx
+++ b/artfynd/A 47044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131894860</v>
       </c>
       <c r="B2" t="n">
-        <v>57825</v>
+        <v>57828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131894964</v>
       </c>
       <c r="B3" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131894809</v>
       </c>
       <c r="B4" t="n">
-        <v>57083</v>
+        <v>57086</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131894922</v>
       </c>
       <c r="B5" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47044-2025 artfynd.xlsx
+++ b/artfynd/A 47044-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131894860</v>
+        <v>131894964</v>
       </c>
       <c r="B2" t="n">
-        <v>57828</v>
+        <v>57912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100001</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,19 +709,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pajsoån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480343</v>
+        <v>480450</v>
       </c>
       <c r="R2" t="n">
-        <v>6674339</v>
+        <v>6674189</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,14 +760,14 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Dun nära funnen dödad tjädertupp</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131894964</v>
+        <v>131894860</v>
       </c>
       <c r="B3" t="n">
-        <v>57907</v>
+        <v>57833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -816,24 +821,19 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pajsoån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480450</v>
+        <v>480343</v>
       </c>
       <c r="R3" t="n">
-        <v>6674189</v>
+        <v>6674339</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,14 +867,14 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Dun nära funnen dödad tjädertupp</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>131894809</v>
       </c>
       <c r="B4" t="n">
-        <v>57086</v>
+        <v>57091</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131894922</v>
       </c>
       <c r="B5" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47044-2025 artfynd.xlsx
+++ b/artfynd/A 47044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131894964</v>
       </c>
       <c r="B2" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131894860</v>
       </c>
       <c r="B3" t="n">
-        <v>57833</v>
+        <v>57835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131894809</v>
       </c>
       <c r="B4" t="n">
-        <v>57091</v>
+        <v>57093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131894922</v>
       </c>
       <c r="B5" t="n">
-        <v>57100</v>
+        <v>57102</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47044-2025 artfynd.xlsx
+++ b/artfynd/A 47044-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131894964</v>
+        <v>131894860</v>
       </c>
       <c r="B2" t="n">
-        <v>57914</v>
+        <v>57835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,24 +709,19 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pajsoån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480450</v>
+        <v>480343</v>
       </c>
       <c r="R2" t="n">
-        <v>6674189</v>
+        <v>6674339</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,14 +755,14 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Dun nära funnen dödad tjädertupp</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131894860</v>
+        <v>131894964</v>
       </c>
       <c r="B3" t="n">
-        <v>57835</v>
+        <v>57914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,16 +793,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -821,19 +816,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pajsoån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480343</v>
+        <v>480450</v>
       </c>
       <c r="R3" t="n">
-        <v>6674339</v>
+        <v>6674189</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,14 +867,14 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Dun nära funnen dödad tjädertupp</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>

--- a/artfynd/A 47044-2025 artfynd.xlsx
+++ b/artfynd/A 47044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131894860</v>
       </c>
       <c r="B2" t="n">
-        <v>57835</v>
+        <v>57869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131894964</v>
       </c>
       <c r="B3" t="n">
-        <v>57914</v>
+        <v>57948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>131894809</v>
       </c>
       <c r="B4" t="n">
-        <v>57093</v>
+        <v>57127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131894922</v>
       </c>
       <c r="B5" t="n">
-        <v>57102</v>
+        <v>57136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47044-2025 artfynd.xlsx
+++ b/artfynd/A 47044-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131894860</v>
+        <v>131894964</v>
       </c>
       <c r="B2" t="n">
-        <v>57869</v>
+        <v>57948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100001</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,19 +709,24 @@
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Pajsoån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480343</v>
+        <v>480450</v>
       </c>
       <c r="R2" t="n">
-        <v>6674339</v>
+        <v>6674189</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,14 +760,14 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Dun nära funnen dödad tjädertupp</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131894964</v>
+        <v>131894860</v>
       </c>
       <c r="B3" t="n">
-        <v>57948</v>
+        <v>57869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -816,24 +821,19 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Pajsoån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480450</v>
+        <v>480343</v>
       </c>
       <c r="R3" t="n">
-        <v>6674189</v>
+        <v>6674339</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,14 +867,14 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Dun nära funnen dödad tjädertupp</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>

--- a/artfynd/A 47044-2025 artfynd.xlsx
+++ b/artfynd/A 47044-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131894860</v>
       </c>
       <c r="B2" t="n">
-        <v>57870</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131894964</v>
       </c>
       <c r="B3" t="n">
-        <v>57949</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,38 +894,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131894809</v>
+        <v>131894922</v>
       </c>
       <c r="B4" t="n">
-        <v>57128</v>
+        <v>57162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>dödad av predator</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -934,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480482</v>
+        <v>480334</v>
       </c>
       <c r="R4" t="n">
-        <v>6674189</v>
+        <v>6674307</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,6 +985,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Duvhöksslagen tjäder</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131894922</v>
+        <v>131894809</v>
       </c>
       <c r="B5" t="n">
-        <v>57137</v>
+        <v>57153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,42 +1027,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>dödad av predator</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1051,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480334</v>
+        <v>480482</v>
       </c>
       <c r="R5" t="n">
-        <v>6674307</v>
+        <v>6674189</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,11 +1092,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Duvhöksslagen tjäder</t>
         </is>
       </c>
       <c r="AD5" t="b">
